--- a/4978_Cuenca_Napo/_raw_reportes_xlsx/IDConfig_65247_completo.xlsx
+++ b/4978_Cuenca_Napo/_raw_reportes_xlsx/IDConfig_65247_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R2550589c972f4f53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rdb2810a9fd8a4b35"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,546 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.2600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.1600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.1600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.0700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.0700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.1700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.1900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.2600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.2800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.3700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.3800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.2900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.2600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.2400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.3400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.3600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>15/08/2026</x:t>
         </x:is>
       </x:c>

--- a/4978_Cuenca_Napo/_raw_reportes_xlsx/IDConfig_65247_completo.xlsx
+++ b/4978_Cuenca_Napo/_raw_reportes_xlsx/IDConfig_65247_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rdb2810a9fd8a4b35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R52a439d65d774501"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,2826 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.6800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.5800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.5800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.5300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.5100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.5700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.5900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.6100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.6300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.6500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.6500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.6900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.6900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.6900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.6900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.6900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.6900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.9100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.9400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.9700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.1700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.1900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.2500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.3400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.3400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.5900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.6400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.7100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.7300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.7700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.8500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.8600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.8700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.0200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.0400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.0700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.0700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.0700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.0700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.0700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.1600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.1800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.1500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.0500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.0500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.0300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.0300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.9900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.9700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.9600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.8700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.8500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.8300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.8300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.7600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.7400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.7200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.5500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.6300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.6500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.7600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.7700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.7800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.7900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.9100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.9500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.9500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.9500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.9500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.1500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.1700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.2400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.2400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.0800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.2500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.2700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.2900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.5300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.5600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.6100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.6300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.5900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.5900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.2700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.2400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.2100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.1800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.0400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.0200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.8500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.8300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.7800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.5600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.5300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.3900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.2900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.2700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.2500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.2600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.2600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.2600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>24/08/2026</x:t>
         </x:is>
       </x:c>
